--- a/public/Data_Cracks and Pothole.xlsx
+++ b/public/Data_Cracks and Pothole.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://protivitimf-my.sharepoint.com/personal/harivardhan_r_protivitiglobal_in/Documents/Desktop/road-survey/Road-Survey/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harivardhan.r\OneDrive - Protiviti Member Firm\Desktop\road-survey\Road-Survey\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{9F23BE07-CD40-43AF-98E6-592833D5BD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD750BCF-772B-4F92-8BAD-0D7F62D97785}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A06471-5890-40FF-A3E9-D9CE325B2985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B467F67D-8F37-4A99-A002-C9E06355F6C0}"/>
   </bookViews>
@@ -248,9 +248,6 @@
     <t>635.jpg</t>
   </si>
   <si>
-    <t>632,jpg</t>
-  </si>
-  <si>
     <t>potholes539.jpg</t>
   </si>
   <si>
@@ -330,6 +327,9 @@
   </si>
   <si>
     <t>damaged-paint1.jpg</t>
+  </si>
+  <si>
+    <t>632.jpg</t>
   </si>
 </sst>
 </file>
@@ -745,6 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -804,7 +805,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -849,7 +850,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -928,10 +929,10 @@
         <v>114</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -972,7 +973,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1013,7 +1014,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1054,7 +1055,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1092,10 +1093,10 @@
         <v>280.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1133,10 +1134,10 @@
         <v>120</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1174,10 +1175,10 @@
         <v>126.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1215,10 +1216,10 @@
         <v>120.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1256,10 +1257,10 @@
         <v>100</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1297,10 +1298,10 @@
         <v>155</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1317,10 +1318,10 @@
         <v>29</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H14" s="6">
         <v>0</v>
@@ -1338,10 +1339,10 @@
         <v>100</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1382,7 +1383,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1423,7 +1424,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1464,7 +1465,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1505,7 +1506,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1546,7 +1547,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1584,10 +1585,10 @@
         <v>113</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1625,10 +1626,10 @@
         <v>124</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1666,10 +1667,10 @@
         <v>124</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1710,7 +1711,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1751,7 +1752,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1792,7 +1793,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1833,7 +1834,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1871,10 +1872,10 @@
         <v>113.5</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1912,10 +1913,10 @@
         <v>115</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1956,7 +1957,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1997,7 +1998,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2038,7 +2039,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2079,7 +2080,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2117,10 +2118,10 @@
         <v>113.5</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2158,10 +2159,10 @@
         <v>121.5</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2199,10 +2200,10 @@
         <v>115</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2240,10 +2241,10 @@
         <v>100</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2281,10 +2282,10 @@
         <v>155</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2301,10 +2302,10 @@
         <v>36</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>43</v>
@@ -2322,10 +2323,10 @@
         <v>100</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2366,7 +2367,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2407,7 +2408,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2448,7 +2449,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2489,7 +2490,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2530,7 +2531,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2568,10 +2569,10 @@
         <v>114</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2609,10 +2610,10 @@
         <v>111.5</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2650,10 +2651,10 @@
         <v>119</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2691,10 +2692,10 @@
         <v>338.5</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2732,10 +2733,10 @@
         <v>331</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2773,10 +2774,10 @@
         <v>303.5</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2814,10 +2815,10 @@
         <v>155</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2834,10 +2835,10 @@
         <v>40</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>43</v>
@@ -2855,10 +2856,10 @@
         <v>100</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2896,10 +2897,10 @@
         <v>100</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2938,7 +2939,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2977,7 +2978,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3017,6 +3018,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N55" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="39.157254"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/public/Data_Cracks and Pothole.xlsx
+++ b/public/Data_Cracks and Pothole.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harivardhan.r\OneDrive - Protiviti Member Firm\Desktop\road-survey\Road-Survey\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A06471-5890-40FF-A3E9-D9CE325B2985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27142D54-6339-4A3C-A811-96D0BA1A977B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B467F67D-8F37-4A99-A002-C9E06355F6C0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="96">
   <si>
     <t>S.No</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>Q2</t>
-  </si>
-  <si>
     <t>Crack</t>
   </si>
   <si>
@@ -98,9 +95,6 @@
     <t>High</t>
   </si>
   <si>
-    <t>Q1</t>
-  </si>
-  <si>
     <t>Bin</t>
   </si>
   <si>
@@ -113,18 +107,12 @@
     <t>Negligible</t>
   </si>
   <si>
-    <t>Q4</t>
-  </si>
-  <si>
     <t>Horizontal Crack</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
-    <t>Q3</t>
-  </si>
-  <si>
     <t> -122.204449</t>
   </si>
   <si>
@@ -320,9 +308,6 @@
     <t>1118.jpg</t>
   </si>
   <si>
-    <t>damaged-paint1</t>
-  </si>
-  <si>
     <t>fadded_paint2.jpg</t>
   </si>
   <si>
@@ -330,6 +315,18 @@
   </si>
   <si>
     <t>632.jpg</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>P1</t>
   </si>
 </sst>
 </file>
@@ -339,7 +336,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,6 +348,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -745,7 +748,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -805,7 +807,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -819,7 +821,7 @@
         <v>-123.639138</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>13</v>
@@ -837,20 +839,20 @@
         <v>14</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L2" s="2">
         <v>320.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N2">
         <f>H2*2</f>
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -864,13 +866,13 @@
         <v>-123.633033</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H3" s="5">
         <v>0.04</v>
@@ -882,13 +884,13 @@
         <v>14</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L3" s="2">
         <v>126.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -905,13 +907,13 @@
         <v>-123.63078</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H4" s="5">
         <v>0.02</v>
@@ -923,16 +925,16 @@
         <v>14</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L4" s="2">
         <v>114</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -943,10 +945,10 @@
         <v>39.156339000000003</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>13</v>
@@ -964,16 +966,16 @@
         <v>14</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L5" s="2">
         <v>289.5</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -987,7 +989,7 @@
         <v>-123.623457</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>13</v>
@@ -1005,16 +1007,16 @@
         <v>14</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L6" s="2">
         <v>315.5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1028,7 +1030,7 @@
         <v>-123.622175</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
@@ -1046,16 +1048,16 @@
         <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L7" s="2">
         <v>311.5</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1069,7 +1071,7 @@
         <v>-123.62041600000001</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>13</v>
@@ -1087,16 +1089,16 @@
         <v>14</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L8" s="2">
         <v>280.5</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1110,13 +1112,13 @@
         <v>-122.200283</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H9" s="5">
         <v>0.02</v>
@@ -1125,19 +1127,19 @@
         <v>0.38</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L9" s="2">
         <v>120</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1151,13 +1153,13 @@
         <v>-122.20026</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H10" s="5">
         <v>0.04</v>
@@ -1166,19 +1168,19 @@
         <v>0.49</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L10" s="2">
         <v>126.5</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1192,13 +1194,13 @@
         <v>-122.203112</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H11" s="5">
         <v>0.03</v>
@@ -1207,19 +1209,19 @@
         <v>0.38</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L11" s="2">
         <v>120.5</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1230,16 +1232,16 @@
         <v>39.785597000000003</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H12" s="5">
         <v>0</v>
@@ -1248,19 +1250,19 @@
         <v>0</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L12" s="2">
         <v>100</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1274,13 +1276,13 @@
         <v>-122.204543</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H13" s="5">
         <v>3</v>
@@ -1289,19 +1291,19 @@
         <v>5</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L13" s="2">
         <v>155</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1315,13 +1317,13 @@
         <v>-122.204714</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H14" s="6">
         <v>0</v>
@@ -1330,19 +1332,19 @@
         <v>0</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L14" s="3">
         <v>100</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1356,7 +1358,7 @@
         <v>-122.205147</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
@@ -1371,19 +1373,19 @@
         <v>0.72</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L15" s="2">
         <v>303.5</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1397,7 +1399,7 @@
         <v>-121.824428</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>13</v>
@@ -1412,19 +1414,19 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L16" s="2">
         <v>295.5</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1438,7 +1440,7 @@
         <v>-121.823227</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>13</v>
@@ -1453,19 +1455,19 @@
         <v>0.83</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L17" s="2">
         <v>328</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1479,7 +1481,7 @@
         <v>-121.820099</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>13</v>
@@ -1494,19 +1496,19 @@
         <v>0.65</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L18" s="2">
         <v>308.5</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1517,10 +1519,10 @@
         <v>39.735169999999997</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>13</v>
@@ -1535,19 +1537,19 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L19" s="2">
         <v>295.5</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1561,13 +1563,13 @@
         <v>-121.817246</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H20" s="5">
         <v>0.02</v>
@@ -1576,19 +1578,19 @@
         <v>0.24</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L20" s="2">
         <v>113</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1602,13 +1604,13 @@
         <v>-121.81593100000001</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H21" s="5">
         <v>0.01</v>
@@ -1617,19 +1619,19 @@
         <v>0.47</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L21" s="2">
         <v>124</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1643,13 +1645,13 @@
         <v>-121.813785</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H22" s="5">
         <v>0.02</v>
@@ -1658,19 +1660,19 @@
         <v>0.46</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L22" s="2">
         <v>124</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1684,7 +1686,7 @@
         <v>-123.24827500000001</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>13</v>
@@ -1699,19 +1701,19 @@
         <v>0.81</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L23" s="2">
         <v>321.5</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1725,7 +1727,7 @@
         <v>-123.24827999999999</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>13</v>
@@ -1740,19 +1742,19 @@
         <v>0.62</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L24" s="2">
         <v>296.5</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1766,7 +1768,7 @@
         <v>-123.248341</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>13</v>
@@ -1781,19 +1783,19 @@
         <v>0.96</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L25" s="2">
         <v>329</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1807,7 +1809,7 @@
         <v>-123.24822</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>13</v>
@@ -1822,19 +1824,19 @@
         <v>0.89</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L26" s="2">
         <v>317.5</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1848,13 +1850,13 @@
         <v>-123.248164</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H27" s="5">
         <v>0.03</v>
@@ -1863,19 +1865,19 @@
         <v>0.24</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L27" s="2">
         <v>113.5</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1889,13 +1891,13 @@
         <v>-123.24418799999999</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H28" s="5">
         <v>0.04</v>
@@ -1904,19 +1906,19 @@
         <v>0.26</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L28" s="2">
         <v>115</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1930,7 +1932,7 @@
         <v>-123.236496</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>13</v>
@@ -1945,19 +1947,19 @@
         <v>0.48</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="L29" s="2">
         <v>279.5</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1971,7 +1973,7 @@
         <v>-119.887596</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>13</v>
@@ -1986,19 +1988,19 @@
         <v>0.85</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="L30" s="2">
         <v>313.5</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2012,7 +2014,7 @@
         <v>-119.857383</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>13</v>
@@ -2027,19 +2029,19 @@
         <v>0.88</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="L31" s="2">
         <v>304.5</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2053,7 +2055,7 @@
         <v>-119.809946</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>13</v>
@@ -2068,19 +2070,19 @@
         <v>0.69</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="L32" s="2">
         <v>308</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2094,13 +2096,13 @@
         <v>-119.794406</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H33" s="5">
         <v>0.04</v>
@@ -2109,19 +2111,19 @@
         <v>0.23</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="L33" s="2">
         <v>113.5</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2135,13 +2137,13 @@
         <v>-119.793921</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H34" s="5">
         <v>0.04</v>
@@ -2150,19 +2152,19 @@
         <v>0.39</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="L34" s="2">
         <v>121.5</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2176,13 +2178,13 @@
         <v>-119.79269600000001</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H35" s="5">
         <v>0.02</v>
@@ -2191,19 +2193,19 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="L35" s="2">
         <v>115</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2217,34 +2219,34 @@
         <v>-119.792517</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="L36" s="2">
         <v>100</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2258,13 +2260,13 @@
         <v>-120.492983</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H37" s="5">
         <v>3</v>
@@ -2276,16 +2278,16 @@
         <v>14</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L37" s="2">
         <v>155</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2299,34 +2301,34 @@
         <v>-120.491694</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J38" s="5" t="s">
         <v>14</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L38" s="2">
         <v>100</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2340,7 +2342,7 @@
         <v>-120.489665</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>13</v>
@@ -2358,16 +2360,16 @@
         <v>14</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L39" s="2">
         <v>295</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2381,7 +2383,7 @@
         <v>-120.48854300000001</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>13</v>
@@ -2399,16 +2401,16 @@
         <v>14</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L40" s="2">
         <v>316.5</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2422,7 +2424,7 @@
         <v>-120.487458</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>13</v>
@@ -2440,16 +2442,16 @@
         <v>14</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L41" s="2">
         <v>323</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2463,7 +2465,7 @@
         <v>-120.48864500000001</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>13</v>
@@ -2481,16 +2483,16 @@
         <v>14</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L42" s="2">
         <v>317</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2504,7 +2506,7 @@
         <v>-120.492013</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>13</v>
@@ -2522,16 +2524,16 @@
         <v>14</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L43" s="2">
         <v>289.5</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2545,13 +2547,13 @@
         <v>-120.81406200000001</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H44" s="5">
         <v>0.05</v>
@@ -2563,16 +2565,16 @@
         <v>14</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L44" s="2">
         <v>114</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2583,16 +2585,16 @@
         <v>37.467675</v>
       </c>
       <c r="D45" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="H45" s="5">
         <v>0.01</v>
@@ -2604,16 +2606,16 @@
         <v>14</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L45" s="2">
         <v>111.5</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2627,13 +2629,13 @@
         <v>-120.81531200000001</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H46" s="5">
         <v>0.02</v>
@@ -2645,16 +2647,16 @@
         <v>14</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L46" s="2">
         <v>119</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2668,7 +2670,7 @@
         <v>-120.81477</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>13</v>
@@ -2686,16 +2688,16 @@
         <v>14</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L47" s="2">
         <v>338.5</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2709,7 +2711,7 @@
         <v>-120.81433699999999</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>13</v>
@@ -2727,16 +2729,16 @@
         <v>14</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L48" s="2">
         <v>331</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2750,7 +2752,7 @@
         <v>-120.81363899999999</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>13</v>
@@ -2768,16 +2770,16 @@
         <v>14</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L49" s="2">
         <v>303.5</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2791,13 +2793,13 @@
         <v>-120.81296</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H50" s="5">
         <v>3</v>
@@ -2809,16 +2811,16 @@
         <v>14</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L50" s="2">
         <v>155</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2832,34 +2834,34 @@
         <v>-120.862257</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L51" s="2">
         <v>100</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2873,34 +2875,34 @@
         <v>-120.86442700000001</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J52" s="5" t="s">
         <v>14</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L52" s="2">
         <v>100</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2911,10 +2913,10 @@
         <v>37.533531000000004</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="2" t="s">
@@ -2930,16 +2932,16 @@
         <v>14</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L53" s="2">
         <v>338.5</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2953,7 +2955,7 @@
         <v>-120.86527599999999</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="2" t="s">
@@ -2969,16 +2971,16 @@
         <v>14</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L54" s="2">
         <v>331</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2992,7 +2994,7 @@
         <v>-120.864552</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="2" t="s">
@@ -3008,23 +3010,18 @@
         <v>14</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L55" s="2">
         <v>303.5</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N55" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="39.157254"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N55" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/public/Data_Cracks and Pothole.xlsx
+++ b/public/Data_Cracks and Pothole.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harivardhan.r\OneDrive - Protiviti Member Firm\Desktop\road-survey\Road-Survey\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27142D54-6339-4A3C-A811-96D0BA1A977B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711D5748-45C2-4961-8C02-EE97FD2937DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B467F67D-8F37-4A99-A002-C9E06355F6C0}"/>
   </bookViews>
@@ -748,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}">
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
@@ -766,7 +766,7 @@
     <col min="13" max="13" width="73.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -807,7 +807,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -830,7 +830,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="5">
-        <v>0.28999999999999998</v>
+        <v>0.435</v>
       </c>
       <c r="I2" s="5">
         <v>0.77</v>
@@ -842,17 +842,17 @@
         <v>92</v>
       </c>
       <c r="L2" s="2">
-        <v>320.5</v>
+        <v>480.75</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>40</v>
       </c>
       <c r="N2">
         <f>H2*2</f>
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -875,7 +875,7 @@
         <v>38</v>
       </c>
       <c r="H3" s="5">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="I3" s="5">
         <v>0.49</v>
@@ -887,13 +887,16 @@
         <v>92</v>
       </c>
       <c r="L3" s="2">
-        <v>126.5</v>
+        <v>189.75</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -915,8 +918,8 @@
       <c r="G4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="5">
-        <v>0.02</v>
+      <c r="H4">
+        <v>0.03</v>
       </c>
       <c r="I4" s="5">
         <v>0.26</v>
@@ -927,14 +930,14 @@
       <c r="K4" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L4" s="2">
-        <v>114</v>
+      <c r="L4">
+        <v>171</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -956,8 +959,8 @@
       <c r="G5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="5">
-        <v>0.11</v>
+      <c r="H5">
+        <v>0.16500000000000001</v>
       </c>
       <c r="I5" s="5">
         <v>0.73</v>
@@ -968,14 +971,14 @@
       <c r="K5" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L5" s="2">
-        <v>289.5</v>
+      <c r="L5">
+        <v>434.25</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -997,8 +1000,8 @@
       <c r="G6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="5">
-        <v>0.23</v>
+      <c r="H6">
+        <v>0.34500000000000003</v>
       </c>
       <c r="I6" s="5">
         <v>0.81</v>
@@ -1009,14 +1012,14 @@
       <c r="K6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L6" s="2">
-        <v>315.5</v>
+      <c r="L6">
+        <v>473.25</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1038,8 +1041,8 @@
       <c r="G7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="5">
-        <v>0.13</v>
+      <c r="H7">
+        <v>0.19500000000000001</v>
       </c>
       <c r="I7" s="5">
         <v>0.92</v>
@@ -1050,14 +1053,14 @@
       <c r="K7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L7" s="2">
-        <v>311.5</v>
+      <c r="L7">
+        <v>467.25</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1079,8 +1082,8 @@
       <c r="G8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="5">
-        <v>0.11</v>
+      <c r="H8">
+        <v>0.16500000000000001</v>
       </c>
       <c r="I8" s="5">
         <v>0.64</v>
@@ -1091,14 +1094,14 @@
       <c r="K8" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L8" s="2">
-        <v>280.5</v>
+      <c r="L8">
+        <v>420.75</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1120,8 +1123,8 @@
       <c r="G9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="5">
-        <v>0.02</v>
+      <c r="H9">
+        <v>0.03</v>
       </c>
       <c r="I9" s="5">
         <v>0.38</v>
@@ -1132,14 +1135,14 @@
       <c r="K9" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L9" s="2">
-        <v>120</v>
+      <c r="L9">
+        <v>180</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1161,8 +1164,8 @@
       <c r="G10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="5">
-        <v>0.04</v>
+      <c r="H10">
+        <v>0.06</v>
       </c>
       <c r="I10" s="5">
         <v>0.49</v>
@@ -1173,14 +1176,14 @@
       <c r="K10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="2">
-        <v>126.5</v>
+      <c r="L10">
+        <v>189.75</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1202,8 +1205,8 @@
       <c r="G11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="5">
-        <v>0.03</v>
+      <c r="H11">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I11" s="5">
         <v>0.38</v>
@@ -1214,14 +1217,14 @@
       <c r="K11" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L11" s="2">
-        <v>120.5</v>
+      <c r="L11">
+        <v>180.75</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1243,7 +1246,7 @@
       <c r="G12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12">
         <v>0</v>
       </c>
       <c r="I12" s="5">
@@ -1255,14 +1258,14 @@
       <c r="K12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L12" s="2">
-        <v>100</v>
+      <c r="L12">
+        <v>150</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1284,8 +1287,8 @@
       <c r="G13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="5">
-        <v>3</v>
+      <c r="H13">
+        <v>4.5</v>
       </c>
       <c r="I13" s="5">
         <v>5</v>
@@ -1296,14 +1299,14 @@
       <c r="K13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L13" s="2">
-        <v>155</v>
+      <c r="L13">
+        <v>232.5</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1325,7 +1328,7 @@
       <c r="G14" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14">
         <v>0</v>
       </c>
       <c r="I14" s="6">
@@ -1337,14 +1340,14 @@
       <c r="K14" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L14" s="3">
-        <v>100</v>
+      <c r="L14">
+        <v>150</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1366,8 +1369,8 @@
       <c r="G15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="5">
-        <v>0.21</v>
+      <c r="H15">
+        <v>0.315</v>
       </c>
       <c r="I15" s="5">
         <v>0.72</v>
@@ -1378,14 +1381,14 @@
       <c r="K15" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L15" s="2">
-        <v>303.5</v>
+      <c r="L15">
+        <v>455.25</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1407,8 +1410,8 @@
       <c r="G16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="5">
-        <v>0.25</v>
+      <c r="H16">
+        <v>0.375</v>
       </c>
       <c r="I16" s="5">
         <v>0.57999999999999996</v>
@@ -1419,8 +1422,8 @@
       <c r="K16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="L16" s="2">
-        <v>295.5</v>
+      <c r="L16">
+        <v>443.25</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>45</v>
@@ -1448,8 +1451,8 @@
       <c r="G17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="5">
-        <v>0.3</v>
+      <c r="H17">
+        <v>0.44999999999999996</v>
       </c>
       <c r="I17" s="5">
         <v>0.83</v>
@@ -1460,8 +1463,8 @@
       <c r="K17" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="L17" s="2">
-        <v>328</v>
+      <c r="L17">
+        <v>492</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>46</v>
@@ -1489,8 +1492,8 @@
       <c r="G18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="5">
-        <v>0.28999999999999998</v>
+      <c r="H18">
+        <v>0.43499999999999994</v>
       </c>
       <c r="I18" s="5">
         <v>0.65</v>
@@ -1501,8 +1504,8 @@
       <c r="K18" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="L18" s="2">
-        <v>308.5</v>
+      <c r="L18">
+        <v>462.75</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>47</v>
@@ -1530,8 +1533,8 @@
       <c r="G19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="5">
-        <v>0.27</v>
+      <c r="H19">
+        <v>0.40500000000000003</v>
       </c>
       <c r="I19" s="5">
         <v>0.55000000000000004</v>
@@ -1542,8 +1545,8 @@
       <c r="K19" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="L19" s="2">
-        <v>295.5</v>
+      <c r="L19">
+        <v>443.25</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>48</v>
@@ -1571,8 +1574,8 @@
       <c r="G20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="5">
-        <v>0.02</v>
+      <c r="H20">
+        <v>0.03</v>
       </c>
       <c r="I20" s="5">
         <v>0.24</v>
@@ -1583,8 +1586,8 @@
       <c r="K20" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="L20" s="2">
-        <v>113</v>
+      <c r="L20">
+        <v>169.5</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>69</v>
@@ -1612,8 +1615,8 @@
       <c r="G21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H21" s="5">
-        <v>0.01</v>
+      <c r="H21">
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="I21" s="5">
         <v>0.47</v>
@@ -1624,8 +1627,8 @@
       <c r="K21" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="L21" s="2">
-        <v>124</v>
+      <c r="L21">
+        <v>186</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>90</v>
@@ -1653,8 +1656,8 @@
       <c r="G22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="5">
-        <v>0.02</v>
+      <c r="H22">
+        <v>0.03</v>
       </c>
       <c r="I22" s="5">
         <v>0.46</v>
@@ -1665,8 +1668,8 @@
       <c r="K22" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="L22" s="2">
-        <v>124</v>
+      <c r="L22">
+        <v>186</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>70</v>
@@ -1694,8 +1697,8 @@
       <c r="G23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="5">
-        <v>0.27</v>
+      <c r="H23">
+        <v>0.40500000000000003</v>
       </c>
       <c r="I23" s="5">
         <v>0.81</v>
@@ -1706,8 +1709,8 @@
       <c r="K23" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L23" s="2">
-        <v>321.5</v>
+      <c r="L23">
+        <v>482.25</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>49</v>
@@ -1735,8 +1738,8 @@
       <c r="G24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H24" s="5">
-        <v>0.23</v>
+      <c r="H24">
+        <v>0.34500000000000003</v>
       </c>
       <c r="I24" s="5">
         <v>0.62</v>
@@ -1747,8 +1750,8 @@
       <c r="K24" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L24" s="2">
-        <v>296.5</v>
+      <c r="L24">
+        <v>444.75</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>50</v>
@@ -1776,8 +1779,8 @@
       <c r="G25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H25" s="5">
-        <v>0.22</v>
+      <c r="H25">
+        <v>0.33</v>
       </c>
       <c r="I25" s="5">
         <v>0.96</v>
@@ -1788,8 +1791,8 @@
       <c r="K25" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L25" s="2">
-        <v>329</v>
+      <c r="L25">
+        <v>493.5</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>51</v>
@@ -1817,8 +1820,8 @@
       <c r="G26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H26" s="5">
-        <v>0.19</v>
+      <c r="H26">
+        <v>0.28500000000000003</v>
       </c>
       <c r="I26" s="5">
         <v>0.89</v>
@@ -1829,8 +1832,8 @@
       <c r="K26" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L26" s="2">
-        <v>317.5</v>
+      <c r="L26">
+        <v>476.25</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>52</v>
@@ -1858,8 +1861,8 @@
       <c r="G27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H27" s="5">
-        <v>0.03</v>
+      <c r="H27">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I27" s="5">
         <v>0.24</v>
@@ -1870,8 +1873,8 @@
       <c r="K27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L27" s="2">
-        <v>113.5</v>
+      <c r="L27">
+        <v>170.25</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>71</v>
@@ -1899,8 +1902,8 @@
       <c r="G28" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H28" s="5">
-        <v>0.04</v>
+      <c r="H28">
+        <v>0.06</v>
       </c>
       <c r="I28" s="5">
         <v>0.26</v>
@@ -1911,8 +1914,8 @@
       <c r="K28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L28" s="2">
-        <v>115</v>
+      <c r="L28">
+        <v>172.5</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>72</v>
@@ -1940,8 +1943,8 @@
       <c r="G29" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="5">
-        <v>0.21</v>
+      <c r="H29">
+        <v>0.315</v>
       </c>
       <c r="I29" s="5">
         <v>0.48</v>
@@ -1952,8 +1955,8 @@
       <c r="K29" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L29" s="2">
-        <v>279.5</v>
+      <c r="L29">
+        <v>419.25</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>53</v>
@@ -1981,8 +1984,8 @@
       <c r="G30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H30" s="5">
-        <v>0.19</v>
+      <c r="H30">
+        <v>0.28500000000000003</v>
       </c>
       <c r="I30" s="5">
         <v>0.85</v>
@@ -1993,8 +1996,8 @@
       <c r="K30" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="L30" s="2">
-        <v>313.5</v>
+      <c r="L30">
+        <v>470.25</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>54</v>
@@ -2022,8 +2025,8 @@
       <c r="G31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H31" s="5">
-        <v>0.11</v>
+      <c r="H31">
+        <v>0.16500000000000001</v>
       </c>
       <c r="I31" s="5">
         <v>0.88</v>
@@ -2034,8 +2037,8 @@
       <c r="K31" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="L31" s="2">
-        <v>304.5</v>
+      <c r="L31">
+        <v>456.75</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>55</v>
@@ -2063,8 +2066,8 @@
       <c r="G32" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="5">
-        <v>0.26</v>
+      <c r="H32">
+        <v>0.39</v>
       </c>
       <c r="I32" s="5">
         <v>0.69</v>
@@ -2075,8 +2078,8 @@
       <c r="K32" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="L32" s="2">
-        <v>308</v>
+      <c r="L32">
+        <v>462</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>56</v>
@@ -2104,8 +2107,8 @@
       <c r="G33" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H33" s="5">
-        <v>0.04</v>
+      <c r="H33">
+        <v>0.06</v>
       </c>
       <c r="I33" s="5">
         <v>0.23</v>
@@ -2116,8 +2119,8 @@
       <c r="K33" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="L33" s="2">
-        <v>113.5</v>
+      <c r="L33">
+        <v>170.25</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>73</v>
@@ -2145,8 +2148,8 @@
       <c r="G34" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H34" s="5">
-        <v>0.04</v>
+      <c r="H34">
+        <v>0.06</v>
       </c>
       <c r="I34" s="5">
         <v>0.39</v>
@@ -2157,8 +2160,8 @@
       <c r="K34" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="L34" s="2">
-        <v>121.5</v>
+      <c r="L34">
+        <v>182.25</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>74</v>
@@ -2186,8 +2189,8 @@
       <c r="G35" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H35" s="5">
-        <v>0.02</v>
+      <c r="H35">
+        <v>0.03</v>
       </c>
       <c r="I35" s="5">
         <v>0.28000000000000003</v>
@@ -2198,8 +2201,8 @@
       <c r="K35" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="L35" s="2">
-        <v>115</v>
+      <c r="L35">
+        <v>172.5</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>75</v>
@@ -2227,7 +2230,7 @@
       <c r="G36" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" t="s">
         <v>39</v>
       </c>
       <c r="I36" s="5" t="s">
@@ -2239,8 +2242,8 @@
       <c r="K36" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="L36" s="2">
-        <v>100</v>
+      <c r="L36">
+        <v>150</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>84</v>
@@ -2268,8 +2271,8 @@
       <c r="G37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H37" s="5">
-        <v>3</v>
+      <c r="H37">
+        <v>4.5</v>
       </c>
       <c r="I37" s="5">
         <v>5</v>
@@ -2280,8 +2283,8 @@
       <c r="K37" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L37" s="2">
-        <v>155</v>
+      <c r="L37">
+        <v>232.5</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>89</v>
@@ -2309,7 +2312,7 @@
       <c r="G38" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" t="s">
         <v>39</v>
       </c>
       <c r="I38" s="5" t="s">
@@ -2321,8 +2324,8 @@
       <c r="K38" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L38" s="2">
-        <v>100</v>
+      <c r="L38">
+        <v>150</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>87</v>
@@ -2350,8 +2353,8 @@
       <c r="G39" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H39" s="5">
-        <v>0.18</v>
+      <c r="H39">
+        <v>0.27</v>
       </c>
       <c r="I39" s="5">
         <v>0.68</v>
@@ -2362,8 +2365,8 @@
       <c r="K39" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L39" s="2">
-        <v>295</v>
+      <c r="L39">
+        <v>442.5</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>57</v>
@@ -2391,8 +2394,8 @@
       <c r="G40" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H40" s="5">
-        <v>0.17</v>
+      <c r="H40">
+        <v>0.255</v>
       </c>
       <c r="I40" s="5">
         <v>0.91</v>
@@ -2403,8 +2406,8 @@
       <c r="K40" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L40" s="2">
-        <v>316.5</v>
+      <c r="L40">
+        <v>474.75</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>58</v>
@@ -2432,8 +2435,8 @@
       <c r="G41" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H41" s="5">
-        <v>0.3</v>
+      <c r="H41">
+        <v>0.44999999999999996</v>
       </c>
       <c r="I41" s="5">
         <v>0.78</v>
@@ -2444,8 +2447,8 @@
       <c r="K41" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L41" s="2">
-        <v>323</v>
+      <c r="L41">
+        <v>484.5</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>60</v>
@@ -2473,8 +2476,8 @@
       <c r="G42" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H42" s="5">
-        <v>0.28000000000000003</v>
+      <c r="H42">
+        <v>0.42000000000000004</v>
       </c>
       <c r="I42" s="5">
         <v>0.75</v>
@@ -2485,8 +2488,8 @@
       <c r="K42" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L42" s="2">
-        <v>317</v>
+      <c r="L42">
+        <v>475.5</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>61</v>
@@ -2514,8 +2517,8 @@
       <c r="G43" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H43" s="5">
-        <v>0.21</v>
+      <c r="H43">
+        <v>0.315</v>
       </c>
       <c r="I43" s="5">
         <v>0.57999999999999996</v>
@@ -2526,8 +2529,8 @@
       <c r="K43" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L43" s="2">
-        <v>289.5</v>
+      <c r="L43">
+        <v>434.25</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>62</v>
@@ -2555,8 +2558,8 @@
       <c r="G44" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H44" s="5">
-        <v>0.05</v>
+      <c r="H44">
+        <v>7.5000000000000011E-2</v>
       </c>
       <c r="I44" s="5">
         <v>0.23</v>
@@ -2567,8 +2570,8 @@
       <c r="K44" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L44" s="2">
-        <v>114</v>
+      <c r="L44">
+        <v>171</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>77</v>
@@ -2596,8 +2599,8 @@
       <c r="G45" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H45" s="5">
-        <v>0.01</v>
+      <c r="H45">
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="I45" s="5">
         <v>0.22</v>
@@ -2608,8 +2611,8 @@
       <c r="K45" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L45" s="2">
-        <v>111.5</v>
+      <c r="L45">
+        <v>167.25</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>76</v>
@@ -2637,8 +2640,8 @@
       <c r="G46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H46" s="5">
-        <v>0.02</v>
+      <c r="H46">
+        <v>0.03</v>
       </c>
       <c r="I46" s="5">
         <v>0.36</v>
@@ -2649,8 +2652,8 @@
       <c r="K46" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L46" s="2">
-        <v>119</v>
+      <c r="L46">
+        <v>178.5</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>78</v>
@@ -2678,8 +2681,8 @@
       <c r="G47" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H47" s="5">
-        <v>0.27</v>
+      <c r="H47">
+        <v>0.40500000000000003</v>
       </c>
       <c r="I47" s="5">
         <v>0.98</v>
@@ -2690,8 +2693,8 @@
       <c r="K47" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L47" s="2">
-        <v>338.5</v>
+      <c r="L47">
+        <v>507.75</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>79</v>
@@ -2719,8 +2722,8 @@
       <c r="G48" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H48" s="5">
-        <v>0.26</v>
+      <c r="H48">
+        <v>0.39</v>
       </c>
       <c r="I48" s="5">
         <v>0.92</v>
@@ -2731,8 +2734,8 @@
       <c r="K48" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L48" s="2">
-        <v>331</v>
+      <c r="L48">
+        <v>496.5</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>80</v>
@@ -2760,8 +2763,8 @@
       <c r="G49" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H49" s="5">
-        <v>0.25</v>
+      <c r="H49">
+        <v>0.375</v>
       </c>
       <c r="I49" s="5">
         <v>0.66</v>
@@ -2772,8 +2775,8 @@
       <c r="K49" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L49" s="2">
-        <v>303.5</v>
+      <c r="L49">
+        <v>455.25</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>81</v>
@@ -2801,8 +2804,8 @@
       <c r="G50" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H50" s="5">
-        <v>3</v>
+      <c r="H50">
+        <v>4.5</v>
       </c>
       <c r="I50" s="5">
         <v>5</v>
@@ -2813,8 +2816,8 @@
       <c r="K50" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L50" s="2">
-        <v>155</v>
+      <c r="L50">
+        <v>232.5</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>90</v>
@@ -2842,7 +2845,7 @@
       <c r="G51" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H51" s="5" t="s">
+      <c r="H51" t="s">
         <v>39</v>
       </c>
       <c r="I51" s="5" t="s">
@@ -2854,8 +2857,8 @@
       <c r="K51" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L51" s="2">
-        <v>100</v>
+      <c r="L51">
+        <v>150</v>
       </c>
       <c r="M51" s="3" t="s">
         <v>88</v>
@@ -2883,7 +2886,7 @@
       <c r="G52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H52" s="5" t="s">
+      <c r="H52" t="s">
         <v>39</v>
       </c>
       <c r="I52" s="5" t="s">
@@ -2895,8 +2898,8 @@
       <c r="K52" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L52" s="2">
-        <v>100</v>
+      <c r="L52">
+        <v>150</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>85</v>
@@ -2922,8 +2925,8 @@
       <c r="G53" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H53" s="5">
-        <v>0.27</v>
+      <c r="H53">
+        <v>0.40500000000000003</v>
       </c>
       <c r="I53" s="5">
         <v>0.98</v>
@@ -2934,8 +2937,8 @@
       <c r="K53" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L53" s="2">
-        <v>338.5</v>
+      <c r="L53">
+        <v>507.75</v>
       </c>
       <c r="M53" s="3" t="s">
         <v>62</v>
@@ -2961,8 +2964,8 @@
       <c r="G54" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H54" s="5">
-        <v>0.26</v>
+      <c r="H54">
+        <v>0.39</v>
       </c>
       <c r="I54" s="5">
         <v>0.92</v>
@@ -2973,8 +2976,8 @@
       <c r="K54" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L54" s="2">
-        <v>331</v>
+      <c r="L54">
+        <v>496.5</v>
       </c>
       <c r="M54" s="3" t="s">
         <v>59</v>
@@ -3000,8 +3003,8 @@
       <c r="G55" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H55" s="5">
-        <v>0.25</v>
+      <c r="H55">
+        <v>0.375</v>
       </c>
       <c r="I55" s="5">
         <v>0.66</v>
@@ -3012,8 +3015,8 @@
       <c r="K55" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L55" s="2">
-        <v>303.5</v>
+      <c r="L55">
+        <v>455.25</v>
       </c>
       <c r="M55" s="3" t="s">
         <v>63</v>

--- a/public/Data_Cracks and Pothole.xlsx
+++ b/public/Data_Cracks and Pothole.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harivardhan.r\OneDrive - Protiviti Member Firm\Desktop\road-survey\Road-Survey\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711D5748-45C2-4961-8C02-EE97FD2937DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E0C782-3CD5-4708-AA46-BCDBE1ABDB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B467F67D-8F37-4A99-A002-C9E06355F6C0}"/>
   </bookViews>
@@ -293,9 +293,6 @@
     <t>Trash1.jpg</t>
   </si>
   <si>
-    <t>Trash3.jpg</t>
-  </si>
-  <si>
     <t>Trash5.jpg</t>
   </si>
   <si>
@@ -327,6 +324,9 @@
   </si>
   <si>
     <t>P1</t>
+  </si>
+  <si>
+    <t>Trash3.png</t>
   </si>
 </sst>
 </file>
@@ -748,6 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -807,7 +808,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -839,7 +840,7 @@
         <v>14</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L2" s="2">
         <v>480.75</v>
@@ -852,7 +853,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -884,7 +885,7 @@
         <v>14</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L3" s="2">
         <v>189.75</v>
@@ -896,7 +897,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -928,16 +929,16 @@
         <v>14</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4">
         <v>171</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -969,7 +970,7 @@
         <v>14</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L5">
         <v>434.25</v>
@@ -978,7 +979,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1010,7 +1011,7 @@
         <v>14</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L6">
         <v>473.25</v>
@@ -1019,7 +1020,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1051,7 +1052,7 @@
         <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L7">
         <v>467.25</v>
@@ -1060,7 +1061,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1092,7 +1093,7 @@
         <v>14</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L8">
         <v>420.75</v>
@@ -1101,7 +1102,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1133,7 +1134,7 @@
         <v>17</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L9">
         <v>180</v>
@@ -1142,7 +1143,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1174,7 +1175,7 @@
         <v>17</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L10">
         <v>189.75</v>
@@ -1183,7 +1184,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1215,7 +1216,7 @@
         <v>17</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L11">
         <v>180.75</v>
@@ -1256,7 +1257,7 @@
         <v>17</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L12">
         <v>150</v>
@@ -1265,7 +1266,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1297,16 +1298,16 @@
         <v>17</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L13">
         <v>232.5</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1338,16 +1339,16 @@
         <v>17</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L14">
         <v>150</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1379,7 +1380,7 @@
         <v>17</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L15">
         <v>455.25</v>
@@ -1388,7 +1389,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1420,7 +1421,7 @@
         <v>21</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L16">
         <v>443.25</v>
@@ -1429,7 +1430,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1461,7 +1462,7 @@
         <v>21</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L17">
         <v>492</v>
@@ -1470,7 +1471,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1502,7 +1503,7 @@
         <v>21</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L18">
         <v>462.75</v>
@@ -1511,7 +1512,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1543,7 +1544,7 @@
         <v>21</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L19">
         <v>443.25</v>
@@ -1552,7 +1553,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1584,7 +1585,7 @@
         <v>21</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L20">
         <v>169.5</v>
@@ -1593,7 +1594,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1625,16 +1626,16 @@
         <v>21</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L21">
         <v>186</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1666,7 +1667,7 @@
         <v>21</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L22">
         <v>186</v>
@@ -1675,7 +1676,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1707,7 +1708,7 @@
         <v>17</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L23">
         <v>482.25</v>
@@ -1716,7 +1717,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1748,7 +1749,7 @@
         <v>17</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L24">
         <v>444.75</v>
@@ -1757,7 +1758,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1789,7 +1790,7 @@
         <v>17</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L25">
         <v>493.5</v>
@@ -1798,7 +1799,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1830,7 +1831,7 @@
         <v>17</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L26">
         <v>476.25</v>
@@ -1839,7 +1840,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1871,7 +1872,7 @@
         <v>17</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L27">
         <v>170.25</v>
@@ -1880,7 +1881,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1912,7 +1913,7 @@
         <v>17</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L28">
         <v>172.5</v>
@@ -1921,7 +1922,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1953,7 +1954,7 @@
         <v>17</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L29">
         <v>419.25</v>
@@ -1962,7 +1963,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1994,7 +1995,7 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L30">
         <v>470.25</v>
@@ -2003,7 +2004,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2035,7 +2036,7 @@
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L31">
         <v>456.75</v>
@@ -2044,7 +2045,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2076,7 +2077,7 @@
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L32">
         <v>462</v>
@@ -2085,7 +2086,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2117,7 +2118,7 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L33">
         <v>170.25</v>
@@ -2126,7 +2127,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2158,7 +2159,7 @@
         <v>23</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L34">
         <v>182.25</v>
@@ -2167,7 +2168,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2199,7 +2200,7 @@
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L35">
         <v>172.5</v>
@@ -2240,16 +2241,16 @@
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L36">
         <v>150</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2281,16 +2282,16 @@
         <v>14</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L37">
         <v>232.5</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2322,16 +2323,16 @@
         <v>14</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L38">
         <v>150</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2363,7 +2364,7 @@
         <v>14</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L39">
         <v>442.5</v>
@@ -2372,7 +2373,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2404,7 +2405,7 @@
         <v>14</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L40">
         <v>474.75</v>
@@ -2413,7 +2414,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2445,7 +2446,7 @@
         <v>14</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L41">
         <v>484.5</v>
@@ -2454,7 +2455,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2486,7 +2487,7 @@
         <v>14</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L42">
         <v>475.5</v>
@@ -2495,7 +2496,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2527,7 +2528,7 @@
         <v>14</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L43">
         <v>434.25</v>
@@ -2536,7 +2537,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2568,7 +2569,7 @@
         <v>14</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L44">
         <v>171</v>
@@ -2577,7 +2578,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2609,7 +2610,7 @@
         <v>14</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L45">
         <v>167.25</v>
@@ -2618,7 +2619,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2650,7 +2651,7 @@
         <v>14</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L46">
         <v>178.5</v>
@@ -2659,7 +2660,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2691,7 +2692,7 @@
         <v>14</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L47">
         <v>507.75</v>
@@ -2700,7 +2701,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2732,7 +2733,7 @@
         <v>14</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L48">
         <v>496.5</v>
@@ -2741,7 +2742,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2773,7 +2774,7 @@
         <v>14</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L49">
         <v>455.25</v>
@@ -2782,7 +2783,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2814,16 +2815,16 @@
         <v>14</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L50">
         <v>232.5</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2855,13 +2856,13 @@
         <v>14</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L51">
         <v>150</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -2896,16 +2897,16 @@
         <v>14</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L52">
         <v>150</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2935,7 +2936,7 @@
         <v>14</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L53">
         <v>507.75</v>
@@ -2944,7 +2945,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2974,7 +2975,7 @@
         <v>14</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L54">
         <v>496.5</v>
@@ -2983,7 +2984,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3013,7 +3014,7 @@
         <v>14</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L55">
         <v>455.25</v>
@@ -3023,7 +3024,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N55" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}"/>
+  <autoFilter ref="A1:N55" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}">
+    <filterColumn colId="12">
+      <filters>
+        <filter val="Trash1.jpg"/>
+        <filter val="Trash3.png"/>
+        <filter val="Trash5.jpg"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/public/Data_Cracks and Pothole.xlsx
+++ b/public/Data_Cracks and Pothole.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harivardhan.r\OneDrive - Protiviti Member Firm\Desktop\road-survey\Road-Survey\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E0C782-3CD5-4708-AA46-BCDBE1ABDB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAC27A3-C044-4CC7-B44C-2D247EFEEFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B467F67D-8F37-4A99-A002-C9E06355F6C0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="97">
   <si>
     <t>S.No</t>
   </si>
@@ -212,24 +212,6 @@
     <t>potholes549.jpg</t>
   </si>
   <si>
-    <t>potholes.548.jpg</t>
-  </si>
-  <si>
-    <t>potholes.547.jpg</t>
-  </si>
-  <si>
-    <t>potholes.541.jpg</t>
-  </si>
-  <si>
-    <t>potholes.546.jpg</t>
-  </si>
-  <si>
-    <t>potholes.545.jpg</t>
-  </si>
-  <si>
-    <t>potholes.544.jpg</t>
-  </si>
-  <si>
     <t>potholes.540.jpg</t>
   </si>
   <si>
@@ -311,9 +293,6 @@
     <t>damaged-paint1.jpg</t>
   </si>
   <si>
-    <t>632.jpg</t>
-  </si>
-  <si>
     <t>P2</t>
   </si>
   <si>
@@ -327,6 +306,30 @@
   </si>
   <si>
     <t>Trash3.png</t>
+  </si>
+  <si>
+    <t>6321.jpg</t>
+  </si>
+  <si>
+    <t>548.jpg</t>
+  </si>
+  <si>
+    <t>547.jpg</t>
+  </si>
+  <si>
+    <t>546.jpg</t>
+  </si>
+  <si>
+    <t>545.jpg</t>
+  </si>
+  <si>
+    <t>544.jpg</t>
+  </si>
+  <si>
+    <t>541.jpg</t>
+  </si>
+  <si>
+    <t>damage_paint3.jpg</t>
   </si>
 </sst>
 </file>
@@ -359,12 +362,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -394,7 +403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -414,6 +423,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -748,7 +758,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:O55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -808,7 +817,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -840,12 +849,12 @@
         <v>14</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L2" s="2">
         <v>480.75</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="9" t="s">
         <v>40</v>
       </c>
       <c r="N2">
@@ -853,7 +862,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -885,19 +894,19 @@
         <v>14</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L3" s="2">
         <v>189.75</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>64</v>
+      <c r="M3" s="9" t="s">
+        <v>58</v>
       </c>
       <c r="O3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -929,16 +938,16 @@
         <v>14</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L4">
         <v>171</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M4" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -970,16 +979,16 @@
         <v>14</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L5">
         <v>434.25</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1011,16 +1020,16 @@
         <v>14</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L6">
         <v>473.25</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1052,16 +1061,16 @@
         <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L7">
         <v>467.25</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="M7" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1093,16 +1102,16 @@
         <v>14</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L8">
         <v>420.75</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1134,16 +1143,16 @@
         <v>17</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L9">
         <v>180</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1175,16 +1184,16 @@
         <v>17</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L10">
         <v>189.75</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M10" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1216,13 +1225,13 @@
         <v>17</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L11">
         <v>180.75</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>68</v>
+      <c r="M11" s="9" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -1257,16 +1266,16 @@
         <v>17</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L12">
         <v>150</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1298,16 +1307,16 @@
         <v>17</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L13">
         <v>232.5</v>
       </c>
-      <c r="M13" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M13" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1324,10 +1333,10 @@
         <v>25</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1339,16 +1348,16 @@
         <v>17</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L14">
         <v>150</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1380,16 +1389,16 @@
         <v>17</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L15">
         <v>455.25</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1421,16 +1430,16 @@
         <v>21</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="L16">
         <v>443.25</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="M16" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1462,16 +1471,16 @@
         <v>21</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="L17">
         <v>492</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="M17" s="9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1503,16 +1512,16 @@
         <v>21</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="L18">
         <v>462.75</v>
       </c>
-      <c r="M18" s="3" t="s">
+      <c r="M18" s="9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1544,16 +1553,16 @@
         <v>21</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="L19">
         <v>443.25</v>
       </c>
-      <c r="M19" s="3" t="s">
+      <c r="M19" s="9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1585,16 +1594,16 @@
         <v>21</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="L20">
         <v>169.5</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M20" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1626,16 +1635,16 @@
         <v>21</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="L21">
         <v>186</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M21" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1667,16 +1676,16 @@
         <v>21</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="L22">
         <v>186</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M22" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1708,16 +1717,16 @@
         <v>17</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L23">
         <v>482.25</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="M23" s="9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1749,16 +1758,16 @@
         <v>17</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L24">
         <v>444.75</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="M24" s="9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1790,16 +1799,16 @@
         <v>17</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L25">
         <v>493.5</v>
       </c>
-      <c r="M25" s="3" t="s">
+      <c r="M25" s="9" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1831,16 +1840,16 @@
         <v>17</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L26">
         <v>476.25</v>
       </c>
-      <c r="M26" s="3" t="s">
+      <c r="M26" s="9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1872,16 +1881,16 @@
         <v>17</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L27">
         <v>170.25</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M27" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1913,16 +1922,16 @@
         <v>17</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L28">
         <v>172.5</v>
       </c>
-      <c r="M28" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M28" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1954,16 +1963,16 @@
         <v>17</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L29">
         <v>419.25</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="M29" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1995,16 +2004,16 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L30">
         <v>470.25</v>
       </c>
-      <c r="M30" s="3" t="s">
+      <c r="M30" s="9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2036,16 +2045,16 @@
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L31">
         <v>456.75</v>
       </c>
-      <c r="M31" s="3" t="s">
+      <c r="M31" s="9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2077,16 +2086,16 @@
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L32">
         <v>462</v>
       </c>
-      <c r="M32" s="3" t="s">
+      <c r="M32" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2118,16 +2127,16 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L33">
         <v>170.25</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M33" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2159,16 +2168,16 @@
         <v>23</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L34">
         <v>182.25</v>
       </c>
-      <c r="M34" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M34" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2200,13 +2209,13 @@
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L35">
         <v>172.5</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>75</v>
+      <c r="M35" s="9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -2241,16 +2250,16 @@
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L36">
         <v>150</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2282,16 +2291,16 @@
         <v>14</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L37">
         <v>232.5</v>
       </c>
-      <c r="M37" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M37" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2308,10 +2317,10 @@
         <v>32</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s">
         <v>39</v>
@@ -2323,16 +2332,16 @@
         <v>14</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L38">
         <v>150</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2364,16 +2373,16 @@
         <v>14</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L39">
         <v>442.5</v>
       </c>
-      <c r="M39" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M39" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2405,16 +2414,16 @@
         <v>14</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L40">
         <v>474.75</v>
       </c>
-      <c r="M40" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M40" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2446,16 +2455,16 @@
         <v>14</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L41">
         <v>484.5</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M41" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2487,16 +2496,16 @@
         <v>14</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L42">
         <v>475.5</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M42" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2528,16 +2537,16 @@
         <v>14</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L43">
         <v>434.25</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M43" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2569,16 +2578,16 @@
         <v>14</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L44">
         <v>171</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M44" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2610,16 +2619,16 @@
         <v>14</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L45">
         <v>167.25</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M45" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2651,16 +2660,16 @@
         <v>14</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L46">
         <v>178.5</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M46" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2692,16 +2701,16 @@
         <v>14</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L47">
         <v>507.75</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M47" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2733,16 +2742,16 @@
         <v>14</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L48">
         <v>496.5</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M48" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2774,16 +2783,16 @@
         <v>14</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L49">
         <v>455.25</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M49" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2815,16 +2824,16 @@
         <v>14</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L50">
         <v>232.5</v>
       </c>
-      <c r="M50" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M50" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2841,10 +2850,10 @@
         <v>36</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H51" t="s">
         <v>39</v>
@@ -2856,13 +2865,13 @@
         <v>14</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L51">
         <v>150</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
@@ -2897,16 +2906,16 @@
         <v>14</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L52">
         <v>150</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2936,16 +2945,16 @@
         <v>14</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L53">
         <v>507.75</v>
       </c>
-      <c r="M53" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M53" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2975,16 +2984,16 @@
         <v>14</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L54">
         <v>496.5</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M54" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3014,25 +3023,17 @@
         <v>14</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L55">
         <v>455.25</v>
       </c>
-      <c r="M55" s="3" t="s">
-        <v>63</v>
+      <c r="M55" s="9" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N55" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}">
-    <filterColumn colId="12">
-      <filters>
-        <filter val="Trash1.jpg"/>
-        <filter val="Trash3.png"/>
-        <filter val="Trash5.jpg"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N55" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/public/Data_Cracks and Pothole.xlsx
+++ b/public/Data_Cracks and Pothole.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harivardhan.r\OneDrive - Protiviti Member Firm\Desktop\road-survey\Road-Survey\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAC27A3-C044-4CC7-B44C-2D247EFEEFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765458E9-DF01-462C-950A-E94839E8B5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B467F67D-8F37-4A99-A002-C9E06355F6C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$55</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="113">
   <si>
     <t>S.No</t>
   </si>
@@ -62,9 +63,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Height</t>
-  </si>
-  <si>
     <t>Width</t>
   </si>
   <si>
@@ -212,9 +210,6 @@
     <t>potholes549.jpg</t>
   </si>
   <si>
-    <t>potholes.540.jpg</t>
-  </si>
-  <si>
     <t>635.jpg</t>
   </si>
   <si>
@@ -230,9 +225,6 @@
     <t>625.jpg</t>
   </si>
   <si>
-    <t>622.jpg</t>
-  </si>
-  <si>
     <t>615.jpg</t>
   </si>
   <si>
@@ -275,9 +267,6 @@
     <t>Trash1.jpg</t>
   </si>
   <si>
-    <t>Trash5.jpg</t>
-  </si>
-  <si>
     <t>1123.jpg</t>
   </si>
   <si>
@@ -305,31 +294,91 @@
     <t>P1</t>
   </si>
   <si>
-    <t>Trash3.png</t>
-  </si>
-  <si>
     <t>6321.jpg</t>
   </si>
   <si>
     <t>548.jpg</t>
   </si>
   <si>
-    <t>547.jpg</t>
-  </si>
-  <si>
     <t>546.jpg</t>
   </si>
   <si>
-    <t>545.jpg</t>
-  </si>
-  <si>
-    <t>544.jpg</t>
-  </si>
-  <si>
     <t>541.jpg</t>
   </si>
   <si>
     <t>damage_paint3.jpg</t>
+  </si>
+  <si>
+    <t>potholes598.jpg</t>
+  </si>
+  <si>
+    <t>540.jpg</t>
+  </si>
+  <si>
+    <t>Width (approx)</t>
+  </si>
+  <si>
+    <t>Depth (approx)</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Clean, dry, circular pothole in center of road</t>
+  </si>
+  <si>
+    <t>Water-filled with loose gravel</t>
+  </si>
+  <si>
+    <t>Water-filled, near intersection</t>
+  </si>
+  <si>
+    <t>Long trench near roadside curb</t>
+  </si>
+  <si>
+    <t>Cluster of multiple potholes</t>
+  </si>
+  <si>
+    <t>544.webp</t>
+  </si>
+  <si>
+    <t>Severely worn road with multiple pothole patches</t>
+  </si>
+  <si>
+    <t>545.webp</t>
+  </si>
+  <si>
+    <t>Irregular, edge-of-road wear</t>
+  </si>
+  <si>
+    <t>Busy urban intersection pothole</t>
+  </si>
+  <si>
+    <t>547.webp</t>
+  </si>
+  <si>
+    <t>City road with pothole clusters</t>
+  </si>
+  <si>
+    <t>Deep water-filled pothole near shoulder</t>
+  </si>
+  <si>
+    <t>618.jpg</t>
+  </si>
+  <si>
+    <t>potholes57.webp</t>
+  </si>
+  <si>
+    <t>622.png</t>
+  </si>
+  <si>
+    <t>Depth</t>
+  </si>
+  <si>
+    <t>Trash3.jpg</t>
+  </si>
+  <si>
+    <t>Trash5.jpeg</t>
   </si>
 </sst>
 </file>
@@ -339,7 +388,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -360,6 +409,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="3">
@@ -403,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -424,6 +478,18 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -758,8 +824,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CE7708-178B-4824-B67D-19590983A603}">
-  <dimension ref="A1:O55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M55"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
@@ -776,7 +842,7 @@
     <col min="13" max="13" width="73.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -799,25 +865,25 @@
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -831,38 +897,36 @@
         <v>-123.639138</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="5">
+        <f>VLOOKUP(M2,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>3</v>
+      </c>
+      <c r="I2" s="5">
+        <f>VLOOKUP(M2,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>24</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0.435</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0.77</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L2" s="2">
         <v>480.75</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2">
-        <f>H2*2</f>
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -876,37 +940,36 @@
         <v>-123.633033</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H3" s="5">
-        <v>0.06</v>
+        <f>VLOOKUP(M3,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>2</v>
       </c>
       <c r="I3" s="5">
-        <v>0.49</v>
+        <f>VLOOKUP(M3,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>14</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L3" s="2">
         <v>189.75</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="O3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -920,34 +983,36 @@
         <v>-123.63078</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4">
-        <v>0.03</v>
+        <v>37</v>
+      </c>
+      <c r="H4" s="5">
+        <f>VLOOKUP(M4,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>2.5</v>
       </c>
       <c r="I4" s="5">
-        <v>0.26</v>
+        <f>VLOOKUP(M4,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>18</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L4">
         <v>171</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -958,37 +1023,39 @@
         <v>39.156339000000003</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5">
+        <f>VLOOKUP(M5,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>7</v>
+      </c>
+      <c r="I5" s="5">
+        <f>VLOOKUP(M5,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>42</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>0.16500000000000001</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0.73</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K5" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L5">
         <v>434.25</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1002,34 +1069,36 @@
         <v>-123.623457</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="5">
+        <f>VLOOKUP(M6,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>4</v>
+      </c>
+      <c r="I6" s="5">
+        <f>VLOOKUP(M6,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>30</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6">
-        <v>0.34500000000000003</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K6" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L6">
         <v>473.25</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1043,34 +1112,36 @@
         <v>-123.622175</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="5">
+        <f>VLOOKUP(M7,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>4</v>
+      </c>
+      <c r="I7" s="5">
+        <f>VLOOKUP(M7,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>24</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7">
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0.92</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L7">
         <v>467.25</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1084,34 +1155,36 @@
         <v>-123.62041600000001</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="5">
+        <f>VLOOKUP(M8,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>4</v>
+      </c>
+      <c r="I8" s="5">
+        <f>VLOOKUP(M8,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>36</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8">
-        <v>0.16500000000000001</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0.64</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L8">
         <v>420.75</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1125,34 +1198,36 @@
         <v>-122.200283</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9">
-        <v>0.03</v>
+        <v>37</v>
+      </c>
+      <c r="H9" s="5">
+        <f>VLOOKUP(M9,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>3</v>
       </c>
       <c r="I9" s="5">
-        <v>0.38</v>
+        <f>VLOOKUP(M9,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>20</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L9">
         <v>180</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1166,34 +1241,36 @@
         <v>-122.20026</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10">
-        <v>0.06</v>
+        <v>37</v>
+      </c>
+      <c r="H10" s="5">
+        <f>VLOOKUP(M10,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>2.5</v>
       </c>
       <c r="I10" s="5">
-        <v>0.49</v>
+        <f>VLOOKUP(M10,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>16</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L10">
         <v>189.75</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1207,34 +1284,36 @@
         <v>-122.203112</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11">
-        <v>4.4999999999999998E-2</v>
+        <v>37</v>
+      </c>
+      <c r="H11" s="5">
+        <f>VLOOKUP(M11,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>2</v>
       </c>
       <c r="I11" s="5">
-        <v>0.38</v>
+        <f>VLOOKUP(M11,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>18</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L11">
         <v>180.75</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1245,37 +1324,37 @@
         <v>39.785597000000003</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="F12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5">
-        <v>0</v>
+      <c r="H12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L12">
         <v>150</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="30">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1289,34 +1368,34 @@
         <v>-122.204543</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13">
-        <v>4.5</v>
+        <v>36</v>
+      </c>
+      <c r="H13" s="5">
+        <v>5</v>
       </c>
       <c r="I13" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L13">
         <v>232.5</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1330,34 +1409,34 @@
         <v>-122.204714</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6">
-        <v>0</v>
+        <v>73</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L14">
         <v>150</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1371,34 +1450,36 @@
         <v>-122.205147</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15">
-        <v>0.315</v>
+        <v>12</v>
+      </c>
+      <c r="H15" s="5">
+        <f>VLOOKUP(M15,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>5</v>
       </c>
       <c r="I15" s="5">
-        <v>0.72</v>
+        <f>VLOOKUP(M15,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>36</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L15">
         <v>455.25</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1412,34 +1493,34 @@
         <v>-121.824428</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16">
-        <v>0.375</v>
+        <v>12</v>
+      </c>
+      <c r="H16" s="5">
+        <v>6</v>
       </c>
       <c r="I16" s="5">
-        <v>0.57999999999999996</v>
+        <v>39</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L16">
         <v>443.25</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1453,34 +1534,36 @@
         <v>-121.823227</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17">
-        <v>0.44999999999999996</v>
+        <v>12</v>
+      </c>
+      <c r="H17" s="5">
+        <f>VLOOKUP(M17,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>6</v>
       </c>
       <c r="I17" s="5">
-        <v>0.83</v>
+        <f>VLOOKUP(M17,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>48</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L17">
         <v>492</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1494,34 +1577,36 @@
         <v>-121.820099</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18">
-        <v>0.43499999999999994</v>
+        <v>12</v>
+      </c>
+      <c r="H18" s="5">
+        <f>VLOOKUP(M18,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>4</v>
       </c>
       <c r="I18" s="5">
-        <v>0.65</v>
+        <f>VLOOKUP(M18,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>30</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L18">
         <v>462.75</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1532,37 +1617,39 @@
         <v>39.735169999999997</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19">
-        <v>0.40500000000000003</v>
+        <v>12</v>
+      </c>
+      <c r="H19" s="5">
+        <f>VLOOKUP(M19,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>5</v>
       </c>
       <c r="I19" s="5">
-        <v>0.55000000000000004</v>
+        <f>VLOOKUP(M19,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>24</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L19">
         <v>443.25</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1576,34 +1663,36 @@
         <v>-121.817246</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20">
-        <v>0.03</v>
+        <v>21</v>
+      </c>
+      <c r="H20" s="5">
+        <f>VLOOKUP(M20,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>1.5</v>
       </c>
       <c r="I20" s="5">
-        <v>0.24</v>
+        <f>VLOOKUP(M20,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>12</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L20">
         <v>169.5</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1617,34 +1706,36 @@
         <v>-121.81593100000001</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H21">
-        <v>1.4999999999999999E-2</v>
+        <v>37</v>
+      </c>
+      <c r="H21" s="5">
+        <f>VLOOKUP(M21,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>2</v>
       </c>
       <c r="I21" s="5">
-        <v>0.47</v>
+        <f>VLOOKUP(M21,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>14</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L21">
         <v>186</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1658,34 +1749,36 @@
         <v>-121.813785</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="5">
+        <f>VLOOKUP(M22,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>3</v>
+      </c>
+      <c r="I22" s="5">
+        <f>VLOOKUP(M22,Sheet2!$B$3:$C$47,2,0)</f>
         <v>22</v>
       </c>
-      <c r="H22">
-        <v>0.03</v>
-      </c>
-      <c r="I22" s="5">
-        <v>0.46</v>
-      </c>
       <c r="J22" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L22">
         <v>186</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1699,34 +1792,36 @@
         <v>-123.24827500000001</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23">
-        <v>0.40500000000000003</v>
+        <v>12</v>
+      </c>
+      <c r="H23" s="5">
+        <f>VLOOKUP(M23,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>6</v>
       </c>
       <c r="I23" s="5">
-        <v>0.81</v>
+        <f>VLOOKUP(M23,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>36</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L23">
         <v>482.25</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1740,34 +1835,36 @@
         <v>-123.24827999999999</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24">
-        <v>0.34500000000000003</v>
+        <v>12</v>
+      </c>
+      <c r="H24" s="5">
+        <f>VLOOKUP(M24,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>4</v>
       </c>
       <c r="I24" s="5">
-        <v>0.62</v>
+        <f>VLOOKUP(M24,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>36</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L24">
         <v>444.75</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1781,34 +1878,36 @@
         <v>-123.248341</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25">
-        <v>0.33</v>
+        <v>12</v>
+      </c>
+      <c r="H25" s="5">
+        <f>VLOOKUP(M25,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>5</v>
       </c>
       <c r="I25" s="5">
-        <v>0.96</v>
+        <f>VLOOKUP(M25,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>36</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L25">
         <v>493.5</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1822,34 +1921,36 @@
         <v>-123.24822</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="5">
+        <f>VLOOKUP(M26,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>4</v>
+      </c>
+      <c r="I26" s="5">
+        <f>VLOOKUP(M26,Sheet2!$B$3:$C$47,2,0)</f>
         <v>30</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26">
-        <v>0.28500000000000003</v>
-      </c>
-      <c r="I26" s="5">
-        <v>0.89</v>
-      </c>
       <c r="J26" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L26">
         <v>476.25</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1863,34 +1964,36 @@
         <v>-123.248164</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H27">
-        <v>4.4999999999999998E-2</v>
+        <v>37</v>
+      </c>
+      <c r="H27" s="5">
+        <f>VLOOKUP(M27,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>3</v>
       </c>
       <c r="I27" s="5">
-        <v>0.24</v>
+        <f>VLOOKUP(M27,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>24</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L27">
         <v>170.25</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1904,34 +2007,36 @@
         <v>-123.24418799999999</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H28">
-        <v>0.06</v>
+        <v>37</v>
+      </c>
+      <c r="H28" s="5">
+        <f>VLOOKUP(M28,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>2.5</v>
       </c>
       <c r="I28" s="5">
-        <v>0.26</v>
+        <f>VLOOKUP(M28,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>16</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L28">
         <v>172.5</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1945,34 +2050,36 @@
         <v>-123.236496</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29">
-        <v>0.315</v>
+        <v>12</v>
+      </c>
+      <c r="H29" s="5">
+        <f>VLOOKUP(M29,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>6</v>
       </c>
       <c r="I29" s="5">
-        <v>0.48</v>
+        <f>VLOOKUP(M29,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>48</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L29">
         <v>419.25</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1986,34 +2093,36 @@
         <v>-119.887596</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30">
-        <v>0.28500000000000003</v>
+        <v>12</v>
+      </c>
+      <c r="H30" s="5">
+        <f>VLOOKUP(M30,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>5</v>
       </c>
       <c r="I30" s="5">
-        <v>0.85</v>
+        <f>VLOOKUP(M30,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>54</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L30">
         <v>470.25</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2027,34 +2136,36 @@
         <v>-119.857383</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31">
-        <v>0.16500000000000001</v>
+        <v>12</v>
+      </c>
+      <c r="H31" s="5">
+        <f>VLOOKUP(M31,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>5</v>
       </c>
       <c r="I31" s="5">
-        <v>0.88</v>
+        <f>VLOOKUP(M31,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>48</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L31">
         <v>456.75</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2068,34 +2179,36 @@
         <v>-119.809946</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32">
-        <v>0.39</v>
+        <v>12</v>
+      </c>
+      <c r="H32" s="5">
+        <f>VLOOKUP(M32,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>3</v>
       </c>
       <c r="I32" s="5">
-        <v>0.69</v>
+        <f>VLOOKUP(M32,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>36</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L32">
         <v>462</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2109,34 +2222,36 @@
         <v>-119.794406</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H33">
-        <v>0.06</v>
+        <v>37</v>
+      </c>
+      <c r="H33" s="5">
+        <f>VLOOKUP(M33,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>2</v>
       </c>
       <c r="I33" s="5">
-        <v>0.23</v>
+        <f>VLOOKUP(M33,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>18</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L33">
         <v>170.25</v>
       </c>
       <c r="M33" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2150,34 +2265,36 @@
         <v>-119.793921</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H34" s="5">
+        <f>VLOOKUP(M34,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="I34" s="5">
+        <f>VLOOKUP(M34,Sheet2!$B$3:$C$47,2,0)</f>
         <v>15</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H34">
-        <v>0.06</v>
-      </c>
-      <c r="I34" s="5">
-        <v>0.39</v>
-      </c>
       <c r="J34" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L34">
         <v>182.25</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2191,34 +2308,36 @@
         <v>-119.79269600000001</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H35">
-        <v>0.03</v>
+        <v>37</v>
+      </c>
+      <c r="H35" s="5">
+        <f>VLOOKUP(M35,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>3</v>
       </c>
       <c r="I35" s="5">
-        <v>0.28000000000000003</v>
+        <f>VLOOKUP(M35,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>20</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L35">
         <v>172.5</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2232,34 +2351,34 @@
         <v>-119.792517</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" t="s">
-        <v>39</v>
+      <c r="H36" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L36">
         <v>150</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="30">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2273,34 +2392,34 @@
         <v>-120.492983</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H37">
-        <v>4.5</v>
+        <v>36</v>
+      </c>
+      <c r="H37" s="5">
+        <v>5</v>
       </c>
       <c r="I37" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L37">
         <v>232.5</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2314,34 +2433,34 @@
         <v>-120.491694</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H38" t="s">
-        <v>39</v>
+        <v>73</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L38">
         <v>150</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2355,34 +2474,36 @@
         <v>-120.489665</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H39" s="5">
+        <f>VLOOKUP(M39,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>6</v>
+      </c>
+      <c r="I39" s="5">
+        <f>VLOOKUP(M39,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>40</v>
+      </c>
+      <c r="J39" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39">
-        <v>0.27</v>
-      </c>
-      <c r="I39" s="5">
-        <v>0.68</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K39" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L39">
         <v>442.5</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2396,34 +2517,36 @@
         <v>-120.48854300000001</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" s="5">
+        <f>VLOOKUP(M40,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>3</v>
+      </c>
+      <c r="I40" s="5">
+        <f>VLOOKUP(M40,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>145</v>
+      </c>
+      <c r="J40" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40">
-        <v>0.255</v>
-      </c>
-      <c r="I40" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K40" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L40">
         <v>474.75</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2437,34 +2560,36 @@
         <v>-120.487458</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" s="5">
+        <f>VLOOKUP(M41,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>5</v>
+      </c>
+      <c r="I41" s="5">
+        <f>VLOOKUP(M41,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>50</v>
+      </c>
+      <c r="J41" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H41">
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="I41" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K41" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L41">
         <v>484.5</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2478,34 +2603,36 @@
         <v>-120.48864500000001</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H42" s="5">
+        <f>VLOOKUP(M42,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>4</v>
+      </c>
+      <c r="I42" s="5">
+        <f>VLOOKUP(M42,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>55</v>
+      </c>
+      <c r="J42" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H42">
-        <v>0.42000000000000004</v>
-      </c>
-      <c r="I42" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K42" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L42">
         <v>475.5</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2519,34 +2646,36 @@
         <v>-120.492013</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H43" s="5">
+        <f>VLOOKUP(M43,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>6</v>
+      </c>
+      <c r="I43" s="5">
+        <f>VLOOKUP(M43,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>48</v>
+      </c>
+      <c r="J43" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H43">
-        <v>0.315</v>
-      </c>
-      <c r="I43" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K43" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L43">
         <v>434.25</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2560,34 +2689,36 @@
         <v>-120.81406200000001</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H44">
-        <v>7.5000000000000011E-2</v>
+        <v>21</v>
+      </c>
+      <c r="H44" s="5">
+        <f>VLOOKUP(M44,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>2</v>
       </c>
       <c r="I44" s="5">
-        <v>0.23</v>
+        <f>VLOOKUP(M44,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>18</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L44">
         <v>171</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2598,37 +2729,39 @@
         <v>37.467675</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H45">
-        <v>1.4999999999999999E-2</v>
+        <v>37</v>
+      </c>
+      <c r="H45" s="5">
+        <f>VLOOKUP(M45,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>1.5</v>
       </c>
       <c r="I45" s="5">
-        <v>0.22</v>
+        <f>VLOOKUP(M45,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>14</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L45">
         <v>167.25</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2642,34 +2775,36 @@
         <v>-120.81531200000001</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H46">
-        <v>0.03</v>
+        <v>21</v>
+      </c>
+      <c r="H46" s="5">
+        <f>VLOOKUP(M46,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>1.5</v>
       </c>
       <c r="I46" s="5">
-        <v>0.36</v>
+        <f>VLOOKUP(M46,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>12</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L46">
         <v>178.5</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2683,34 +2818,36 @@
         <v>-120.81477</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H47" s="5">
+        <f>VLOOKUP(M47,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>5</v>
+      </c>
+      <c r="I47" s="5">
+        <f>VLOOKUP(M47,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>27</v>
+      </c>
+      <c r="J47" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H47">
-        <v>0.40500000000000003</v>
-      </c>
-      <c r="I47" s="5">
-        <v>0.98</v>
-      </c>
-      <c r="J47" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K47" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L47">
         <v>507.75</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2724,34 +2861,36 @@
         <v>-120.81433699999999</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H48" s="5">
+        <f>VLOOKUP(M48,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>6</v>
+      </c>
+      <c r="I48" s="5">
+        <f>VLOOKUP(M48,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>26</v>
+      </c>
+      <c r="J48" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H48">
-        <v>0.39</v>
-      </c>
-      <c r="I48" s="5">
-        <v>0.92</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K48" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L48">
         <v>496.5</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2765,34 +2904,36 @@
         <v>-120.81363899999999</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" s="5">
+        <f>VLOOKUP(M49,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>5</v>
+      </c>
+      <c r="I49" s="5">
+        <f>VLOOKUP(M49,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>22</v>
+      </c>
+      <c r="J49" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H49">
-        <v>0.375</v>
-      </c>
-      <c r="I49" s="5">
-        <v>0.66</v>
-      </c>
-      <c r="J49" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K49" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L49">
         <v>455.25</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="30">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2806,34 +2947,34 @@
         <v>-120.81296</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H50">
-        <v>4.5</v>
+        <v>36</v>
+      </c>
+      <c r="H50" s="5">
+        <v>5</v>
       </c>
       <c r="I50" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L50">
         <v>232.5</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2847,34 +2988,34 @@
         <v>-120.862257</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H51" t="s">
-        <v>39</v>
+        <v>73</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L51">
         <v>150</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2888,34 +3029,34 @@
         <v>-120.86442700000001</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F52" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G52" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H52" t="s">
-        <v>39</v>
+      <c r="H52" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L52">
         <v>150</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2926,35 +3067,37 @@
         <v>37.533531000000004</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" s="5">
+        <f>VLOOKUP(M53,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>4</v>
+      </c>
+      <c r="I53" s="5">
+        <f>VLOOKUP(M53,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>170</v>
+      </c>
+      <c r="J53" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H53">
-        <v>0.40500000000000003</v>
-      </c>
-      <c r="I53" s="5">
-        <v>0.98</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K53" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L53">
         <v>507.75</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2968,32 +3111,34 @@
         <v>-120.86527599999999</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H54" s="5">
+        <f>VLOOKUP(M54,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>6</v>
+      </c>
+      <c r="I54" s="5">
+        <f>VLOOKUP(M54,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>120</v>
+      </c>
+      <c r="J54" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H54">
-        <v>0.39</v>
-      </c>
-      <c r="I54" s="5">
-        <v>0.92</v>
-      </c>
-      <c r="J54" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K54" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L54">
         <v>496.5</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3007,29 +3152,31 @@
         <v>-120.864552</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H55" s="5">
+        <f>VLOOKUP(M55,Sheet2!$B$3:$D$47,3,0)</f>
+        <v>6</v>
+      </c>
+      <c r="I55" s="5">
+        <f>VLOOKUP(M55,Sheet2!$B$3:$C$47,2,0)</f>
+        <v>75</v>
+      </c>
+      <c r="J55" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H55">
-        <v>0.375</v>
-      </c>
-      <c r="I55" s="5">
-        <v>0.66</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="K55" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L55">
         <v>455.25</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3038,4 +3185,584 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D990285-FB8E-4C1F-A409-C6E873EC3E07}">
+  <dimension ref="B2:F47"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6">
+      <c r="B2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="30">
+      <c r="B3" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="13">
+        <v>22</v>
+      </c>
+      <c r="D3" s="13">
+        <v>5</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="13">
+        <v>26</v>
+      </c>
+      <c r="D4" s="13">
+        <v>6</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="13">
+        <v>27</v>
+      </c>
+      <c r="D5" s="13">
+        <v>5</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="13">
+        <v>75</v>
+      </c>
+      <c r="D6" s="13">
+        <v>6</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="13">
+        <v>120</v>
+      </c>
+      <c r="D7" s="13">
+        <v>6</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="30">
+      <c r="B8" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="13">
+        <v>170</v>
+      </c>
+      <c r="D8" s="13">
+        <v>4</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="13">
+        <v>55</v>
+      </c>
+      <c r="D9" s="13">
+        <v>4</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="13">
+        <v>50</v>
+      </c>
+      <c r="D10" s="13">
+        <v>5</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="13">
+        <v>145</v>
+      </c>
+      <c r="D11" s="13">
+        <v>3</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="30">
+      <c r="B12" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="13">
+        <v>40</v>
+      </c>
+      <c r="D12" s="13">
+        <v>6</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="11">
+        <v>36</v>
+      </c>
+      <c r="D13" s="11">
+        <v>6</v>
+      </c>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="11">
+        <v>24</v>
+      </c>
+      <c r="D14" s="11">
+        <v>5</v>
+      </c>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="11">
+        <v>30</v>
+      </c>
+      <c r="D15" s="11">
+        <v>4</v>
+      </c>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="11">
+        <v>48</v>
+      </c>
+      <c r="D16" s="11">
+        <v>6</v>
+      </c>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="11">
+        <v>36</v>
+      </c>
+      <c r="D17" s="11">
+        <v>5</v>
+      </c>
+      <c r="F17" s="11"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="11">
+        <v>24</v>
+      </c>
+      <c r="D18" s="11">
+        <v>4</v>
+      </c>
+      <c r="F18" s="11"/>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="11">
+        <v>30</v>
+      </c>
+      <c r="D19" s="11">
+        <v>4</v>
+      </c>
+      <c r="F19" s="11"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="11">
+        <v>42</v>
+      </c>
+      <c r="D20" s="11">
+        <v>7</v>
+      </c>
+      <c r="F20" s="11"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="11">
+        <v>48</v>
+      </c>
+      <c r="D21" s="11">
+        <v>6</v>
+      </c>
+      <c r="F21" s="11"/>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22">
+        <v>30</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23">
+        <v>24</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24">
+        <v>36</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25">
+        <v>36</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26">
+        <v>48</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27">
+        <v>54</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28">
+        <v>48</v>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29">
+        <v>30</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30">
+        <v>36</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31">
+        <v>36</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="11">
+        <v>12</v>
+      </c>
+      <c r="D32" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="F32" s="11"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="11">
+        <v>18</v>
+      </c>
+      <c r="D33" s="11">
+        <v>2</v>
+      </c>
+      <c r="F33" s="11"/>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="11">
+        <v>14</v>
+      </c>
+      <c r="D34" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="F34" s="11"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="11">
+        <v>20</v>
+      </c>
+      <c r="D35" s="11">
+        <v>3</v>
+      </c>
+      <c r="F35" s="11"/>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="11">
+        <v>15</v>
+      </c>
+      <c r="D36" s="11">
+        <v>2</v>
+      </c>
+      <c r="F36" s="11"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="11">
+        <v>18</v>
+      </c>
+      <c r="D37" s="11">
+        <v>2</v>
+      </c>
+      <c r="F37" s="11"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="11">
+        <v>16</v>
+      </c>
+      <c r="D38" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F38" s="11"/>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="11">
+        <v>22</v>
+      </c>
+      <c r="D39" s="11">
+        <v>3</v>
+      </c>
+      <c r="F39" s="11"/>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="11">
+        <v>14</v>
+      </c>
+      <c r="D40" s="11">
+        <v>2</v>
+      </c>
+      <c r="F40" s="11"/>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" s="11">
+        <v>24</v>
+      </c>
+      <c r="D41" s="11">
+        <v>3</v>
+      </c>
+      <c r="F41" s="11"/>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42" s="11">
+        <v>12</v>
+      </c>
+      <c r="D42" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="F42" s="11"/>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="11">
+        <v>18</v>
+      </c>
+      <c r="D43" s="11">
+        <v>2</v>
+      </c>
+      <c r="F43" s="11"/>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" s="11">
+        <v>16</v>
+      </c>
+      <c r="D44" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F44" s="11"/>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="11">
+        <v>20</v>
+      </c>
+      <c r="D45" s="11">
+        <v>3</v>
+      </c>
+      <c r="F45" s="11"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="11">
+        <v>14</v>
+      </c>
+      <c r="D46" s="11">
+        <v>2</v>
+      </c>
+      <c r="F46" s="11"/>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="B47" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" s="11">
+        <v>18</v>
+      </c>
+      <c r="D47" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F47" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>